--- a/VerveStacks_EST/vt_EST_PRI_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_PRI_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29CECFA-B7D8-4CE6-89C0-CD92318317B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3876B6-8CF1-4EE2-9CFB-89671C7A9BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="28">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -114,6 +114,12 @@
   </si>
   <si>
     <t>ELC</t>
+  </si>
+  <si>
+    <t>Trd_electricity import_ru</t>
+  </si>
+  <si>
+    <t>Trd_electricity export_ru</t>
   </si>
 </sst>
 </file>
@@ -460,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:R8"/>
+  <dimension ref="A3:S10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
@@ -469,7 +475,7 @@
     <col min="11" max="11" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -481,7 +487,7 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -522,16 +528,19 @@
         <v>2022</v>
       </c>
       <c r="P4" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="s">
+        <v>2025</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0</v>
+      </c>
+      <c r="R4" t="s">
         <v>23</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -554,19 +563,22 @@
         <v>25</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>6.86</v>
       </c>
       <c r="P5">
+        <v>4.68</v>
+      </c>
+      <c r="Q5">
         <v>3</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>1000</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -592,21 +604,24 @@
         <v>0</v>
       </c>
       <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
         <v>3</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>1000</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
@@ -618,30 +633,33 @@
         <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" t="s">
         <v>25</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
         <v>3</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>1000</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>8</v>
@@ -653,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="I8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" t="s">
         <v>25</v>
@@ -662,12 +680,91 @@
         <v>0</v>
       </c>
       <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
         <v>3</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>1000</v>
       </c>
-      <c r="R8">
+      <c r="S8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O9">
+        <v>3.76</v>
+      </c>
+      <c r="P9">
+        <v>1.64</v>
+      </c>
+      <c r="Q9">
+        <v>3</v>
+      </c>
+      <c r="R9">
+        <v>1000</v>
+      </c>
+      <c r="S9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" t="s">
+        <v>25</v>
+      </c>
+      <c r="O10">
+        <v>2.08</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>3</v>
+      </c>
+      <c r="R10">
+        <v>1000</v>
+      </c>
+      <c r="S10">
         <v>50</v>
       </c>
     </row>

--- a/VerveStacks_EST/vt_EST_PRI_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_PRI_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3876B6-8CF1-4EE2-9CFB-89671C7A9BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F3B2A1-9065-4283-B66F-E896CF6EC034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,9 +86,6 @@
     <t>Trd_electricity export_fi</t>
   </si>
   <si>
-    <t>~FI_T: USD21~FX~ACT_BND</t>
-  </si>
-  <si>
     <t>Process</t>
   </si>
   <si>
@@ -120,6 +117,9 @@
   </si>
   <si>
     <t>Trd_electricity export_ru</t>
+  </si>
+  <si>
+    <t>~FI_T: USD21~UP~ACT_BND</t>
   </si>
 </sst>
 </file>
@@ -480,7 +480,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -507,22 +507,22 @@
         <v>6</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" t="s">
         <v>19</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>20</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="O4" s="2">
         <v>2022</v>
@@ -534,10 +534,10 @@
         <v>0</v>
       </c>
       <c r="R4" t="s">
+        <v>22</v>
+      </c>
+      <c r="S4" t="s">
         <v>23</v>
-      </c>
-      <c r="S4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -560,7 +560,7 @@
         <v>12</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O5">
         <v>6.86</v>
@@ -598,7 +598,7 @@
         <v>13</v>
       </c>
       <c r="K6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
@@ -633,10 +633,10 @@
         <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -674,7 +674,7 @@
         <v>15</v>
       </c>
       <c r="J8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -712,7 +712,7 @@
         <v>14</v>
       </c>
       <c r="J9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O9">
         <v>3.76</v>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>8</v>
@@ -747,10 +747,10 @@
         <v>10</v>
       </c>
       <c r="I10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O10">
         <v>2.08</v>

--- a/VerveStacks_EST/vt_EST_PRI_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_PRI_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F3B2A1-9065-4283-B66F-E896CF6EC034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2651EFD4-BE49-49A7-8355-5B44941AB4E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -119,7 +119,7 @@
     <t>Trd_electricity export_ru</t>
   </si>
   <si>
-    <t>~FI_T: USD21~UP~ACT_BND</t>
+    <t>~FI_T: USD21~LO~ACT_BND</t>
   </si>
 </sst>
 </file>

--- a/VerveStacks_EST/vt_EST_PRI_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_PRI_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2651EFD4-BE49-49A7-8355-5B44941AB4E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA45C75-4BC8-4FCB-8357-FCFA2D0530F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
     <t>Trd_electricity export_ru</t>
   </si>
   <si>
-    <t>~FI_T: USD21~LO~ACT_BND</t>
+    <t>~FI_T: USD21~UP~ACT_BND</t>
   </si>
 </sst>
 </file>
@@ -562,6 +562,9 @@
       <c r="K5" t="s">
         <v>24</v>
       </c>
+      <c r="M5">
+        <v>8.76</v>
+      </c>
       <c r="O5">
         <v>6.86</v>
       </c>
@@ -600,6 +603,9 @@
       <c r="K6" t="s">
         <v>24</v>
       </c>
+      <c r="M6">
+        <v>8.76</v>
+      </c>
       <c r="O6">
         <v>0</v>
       </c>
@@ -638,6 +644,9 @@
       <c r="K7" t="s">
         <v>24</v>
       </c>
+      <c r="M7">
+        <v>8.76</v>
+      </c>
       <c r="O7">
         <v>0</v>
       </c>
@@ -676,6 +685,9 @@
       <c r="J8" t="s">
         <v>24</v>
       </c>
+      <c r="M8">
+        <v>8.76</v>
+      </c>
       <c r="O8">
         <v>0</v>
       </c>
@@ -714,6 +726,9 @@
       <c r="J9" t="s">
         <v>24</v>
       </c>
+      <c r="M9">
+        <v>8.76</v>
+      </c>
       <c r="O9">
         <v>3.76</v>
       </c>
@@ -751,6 +766,9 @@
       </c>
       <c r="K10" t="s">
         <v>24</v>
+      </c>
+      <c r="M10">
+        <v>8.76</v>
       </c>
       <c r="O10">
         <v>2.08</v>

--- a/VerveStacks_EST/vt_EST_PRI_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_PRI_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA45C75-4BC8-4FCB-8357-FCFA2D0530F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA6497E-2E6B-4C3E-8A36-BC0BF2EC8EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="29">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>Trd_electricity export_fi</t>
+  </si>
+  <si>
+    <t>~FI_T: USD21~FX~ACT_BND</t>
   </si>
   <si>
     <t>Process</t>
@@ -466,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:S10"/>
+  <dimension ref="A3:S13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
@@ -480,7 +483,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -507,22 +510,22 @@
         <v>6</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O4" s="2">
         <v>2022</v>
@@ -534,10 +537,10 @@
         <v>0</v>
       </c>
       <c r="R4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -560,7 +563,7 @@
         <v>12</v>
       </c>
       <c r="K5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M5">
         <v>8.76</v>
@@ -601,7 +604,7 @@
         <v>13</v>
       </c>
       <c r="K6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M6">
         <v>8.76</v>
@@ -627,7 +630,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
@@ -639,10 +642,10 @@
         <v>10</v>
       </c>
       <c r="I7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" t="s">
         <v>25</v>
-      </c>
-      <c r="K7" t="s">
-        <v>24</v>
       </c>
       <c r="M7">
         <v>8.76</v>
@@ -679,32 +682,8 @@
       <c r="F8" t="s">
         <v>10</v>
       </c>
-      <c r="I8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" t="s">
-        <v>24</v>
-      </c>
-      <c r="M8">
-        <v>8.76</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>3</v>
-      </c>
-      <c r="R8">
-        <v>1000</v>
-      </c>
-      <c r="S8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -720,29 +699,8 @@
       <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="I9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9">
-        <v>8.76</v>
-      </c>
-      <c r="O9">
-        <v>3.76</v>
-      </c>
-      <c r="P9">
-        <v>1.64</v>
-      </c>
-      <c r="Q9">
-        <v>3</v>
-      </c>
-      <c r="R9">
-        <v>1000</v>
-      </c>
-      <c r="S9">
-        <v>50</v>
+      <c r="K9" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -750,7 +708,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>8</v>
@@ -761,28 +719,115 @@
       <c r="F10" t="s">
         <v>10</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L10" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O10" s="2">
+        <v>2022</v>
+      </c>
+      <c r="P10" s="2">
+        <v>2025</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0</v>
+      </c>
+      <c r="R10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" t="s">
         <v>25</v>
       </c>
-      <c r="K10" t="s">
-        <v>24</v>
-      </c>
-      <c r="M10">
+      <c r="M11">
         <v>8.76</v>
       </c>
-      <c r="O10">
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>3</v>
+      </c>
+      <c r="R11">
+        <v>1000</v>
+      </c>
+      <c r="S11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12">
+        <v>8.76</v>
+      </c>
+      <c r="O12">
+        <v>3.76</v>
+      </c>
+      <c r="P12">
+        <v>1.64</v>
+      </c>
+      <c r="Q12">
+        <v>3</v>
+      </c>
+      <c r="R12">
+        <v>1000</v>
+      </c>
+      <c r="S12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13">
+        <v>8.76</v>
+      </c>
+      <c r="O13">
         <v>2.08</v>
       </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
         <v>3</v>
       </c>
-      <c r="R10">
+      <c r="R13">
         <v>1000</v>
       </c>
-      <c r="S10">
+      <c r="S13">
         <v>50</v>
       </c>
     </row>

--- a/VerveStacks_EST/vt_EST_PRI_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_PRI_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA6497E-2E6B-4C3E-8A36-BC0BF2EC8EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A72CB6-E10F-404F-9F3B-F77B73879FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="30">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -123,13 +123,16 @@
   </si>
   <si>
     <t>~FI_T: USD21~UP~ACT_BND</t>
+  </si>
+  <si>
+    <t>NCAP_AFC!!!!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,6 +154,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="186"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -184,10 +194,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Heading 3" xfId="1" builtinId="18"/>
@@ -469,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:S13"/>
+  <dimension ref="A3:V13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
@@ -478,7 +489,7 @@
     <col min="11" max="11" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -490,7 +501,7 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -542,8 +553,11 @@
       <c r="S4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="V4" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -584,7 +598,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -625,7 +639,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -666,7 +680,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -683,7 +697,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -703,7 +717,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -753,7 +767,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I11" t="s">
         <v>15</v>
       </c>
@@ -779,7 +793,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I12" t="s">
         <v>14</v>
       </c>
@@ -805,7 +819,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I13" t="s">
         <v>27</v>
       </c>

--- a/VerveStacks_EST/vt_EST_PRI_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_PRI_v1.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A72CB6-E10F-404F-9F3B-F77B73879FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB0E70A-7094-49C8-B7D1-63FF7675FA85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="35">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -126,6 +127,21 @@
   </si>
   <si>
     <t>NCAP_AFC!!!!</t>
+  </si>
+  <si>
+    <t>curr</t>
+  </si>
+  <si>
+    <t>eur19</t>
+  </si>
+  <si>
+    <t>~FI_T: UP~ACT_BND</t>
+  </si>
+  <si>
+    <t>ncap_pasti</t>
+  </si>
+  <si>
+    <t>~FI_T: FX~ACT_BND</t>
   </si>
 </sst>
 </file>
@@ -481,15 +497,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A3:V13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -501,7 +517,7 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -557,7 +573,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -598,7 +614,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -639,7 +655,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -680,7 +696,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -697,7 +713,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -717,7 +733,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -767,7 +783,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="I11" t="s">
         <v>15</v>
       </c>
@@ -793,7 +809,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="I12" t="s">
         <v>14</v>
       </c>
@@ -819,7 +835,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="I13" t="s">
         <v>27</v>
       </c>
@@ -843,6 +859,445 @@
       </c>
       <c r="S13">
         <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C768FA58-8399-45BE-8875-71A71258D648}">
+  <dimension ref="A3:V13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O4" s="2">
+        <v>2022</v>
+      </c>
+      <c r="P4" s="2">
+        <v>2025</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0</v>
+      </c>
+      <c r="R4" t="s">
+        <v>23</v>
+      </c>
+      <c r="S4" t="s">
+        <v>24</v>
+      </c>
+      <c r="T4" t="s">
+        <v>33</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5">
+        <v>8.76</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>6.86</v>
+      </c>
+      <c r="P5">
+        <v>4.68</v>
+      </c>
+      <c r="Q5">
+        <v>3</v>
+      </c>
+      <c r="R5">
+        <v>1000</v>
+      </c>
+      <c r="S5">
+        <v>50</v>
+      </c>
+      <c r="T5">
+        <v>1.016</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6">
+        <v>8.76</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>3</v>
+      </c>
+      <c r="R6">
+        <v>1000</v>
+      </c>
+      <c r="S6">
+        <v>50</v>
+      </c>
+      <c r="T6">
+        <v>1.204</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7">
+        <v>8.76</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>3</v>
+      </c>
+      <c r="R7">
+        <v>1000</v>
+      </c>
+      <c r="S7">
+        <v>50</v>
+      </c>
+      <c r="T7">
+        <v>0.63500000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L10" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O10" s="2">
+        <v>2022</v>
+      </c>
+      <c r="P10" s="2">
+        <v>2025</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0</v>
+      </c>
+      <c r="R10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S10" t="s">
+        <v>24</v>
+      </c>
+      <c r="T10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="H11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11">
+        <v>8.76</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>3</v>
+      </c>
+      <c r="R11">
+        <v>1000</v>
+      </c>
+      <c r="S11">
+        <v>50</v>
+      </c>
+      <c r="T11">
+        <v>1.016</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="H12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12">
+        <v>8.76</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>3.76</v>
+      </c>
+      <c r="P12">
+        <v>1.64</v>
+      </c>
+      <c r="Q12">
+        <v>3</v>
+      </c>
+      <c r="R12">
+        <v>1000</v>
+      </c>
+      <c r="S12">
+        <v>50</v>
+      </c>
+      <c r="T12">
+        <v>0.99850000000000005</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="H13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13">
+        <v>8.76</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>2.08</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>3</v>
+      </c>
+      <c r="R13">
+        <v>1000</v>
+      </c>
+      <c r="S13">
+        <v>50</v>
+      </c>
+      <c r="T13">
+        <v>0.63</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/vt_EST_PRI_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_PRI_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB0E70A-7094-49C8-B7D1-63FF7675FA85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C750E11-AF57-47BD-955A-0FC101559EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="35">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -129,19 +129,19 @@
     <t>NCAP_AFC!!!!</t>
   </si>
   <si>
+    <t>~FI_T</t>
+  </si>
+  <si>
     <t>curr</t>
   </si>
   <si>
     <t>eur19</t>
   </si>
   <si>
-    <t>~FI_T: UP~ACT_BND</t>
-  </si>
-  <si>
     <t>ncap_pasti</t>
   </si>
   <si>
-    <t>~FI_T: FX~ACT_BND</t>
+    <t>~FI_T: UP</t>
   </si>
 </sst>
 </file>
@@ -868,29 +868,31 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C768FA58-8399-45BE-8875-71A71258D648}">
-  <dimension ref="A3:V13"/>
+  <dimension ref="A3:T17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="23.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.90625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.1796875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -910,7 +912,7 @@
         <v>6</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>17</v>
@@ -931,28 +933,22 @@
         <v>22</v>
       </c>
       <c r="O4" s="2">
-        <v>2022</v>
-      </c>
-      <c r="P4" s="2">
-        <v>2025</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>24</v>
       </c>
       <c r="R4" t="s">
-        <v>23</v>
-      </c>
-      <c r="S4" t="s">
-        <v>24</v>
-      </c>
-      <c r="T4" t="s">
         <v>33</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -969,7 +965,7 @@
         <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" t="s">
         <v>12</v>
@@ -984,25 +980,19 @@
         <v>0</v>
       </c>
       <c r="O5">
-        <v>6.86</v>
+        <v>3</v>
       </c>
       <c r="P5">
-        <v>4.68</v>
+        <v>1000</v>
       </c>
       <c r="Q5">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="R5">
-        <v>1000</v>
-      </c>
-      <c r="S5">
-        <v>50</v>
-      </c>
-      <c r="T5">
         <v>1.016</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1019,7 +1009,7 @@
         <v>10</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" t="s">
         <v>13</v>
@@ -1034,30 +1024,24 @@
         <v>0</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Q6">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="R6">
-        <v>1000</v>
-      </c>
-      <c r="S6">
-        <v>50</v>
-      </c>
-      <c r="T6">
         <v>1.204</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
@@ -1069,45 +1053,15 @@
         <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7">
-        <v>8.76</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>3</v>
-      </c>
-      <c r="R7">
-        <v>1000</v>
-      </c>
-      <c r="S7">
-        <v>50</v>
-      </c>
-      <c r="T7">
-        <v>0.63500000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>8</v>
@@ -1119,44 +1073,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
+    <row r="9" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="K9" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="H10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>17</v>
@@ -1177,27 +1101,21 @@
         <v>22</v>
       </c>
       <c r="O10" s="2">
-        <v>2022</v>
-      </c>
-      <c r="P10" s="2">
-        <v>2025</v>
-      </c>
-      <c r="Q10" s="2">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>24</v>
       </c>
       <c r="R10" t="s">
-        <v>23</v>
-      </c>
-      <c r="S10" t="s">
-        <v>24</v>
-      </c>
-      <c r="T10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="H11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
@@ -1212,27 +1130,21 @@
         <v>0</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="R11">
-        <v>1000</v>
-      </c>
-      <c r="S11">
-        <v>50</v>
-      </c>
-      <c r="T11">
         <v>1.016</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="H12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" t="s">
         <v>14</v>
@@ -1247,57 +1159,55 @@
         <v>0</v>
       </c>
       <c r="O12">
-        <v>3.76</v>
+        <v>3</v>
       </c>
       <c r="P12">
-        <v>1.64</v>
+        <v>1000</v>
       </c>
       <c r="Q12">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="R12">
-        <v>1000</v>
-      </c>
-      <c r="S12">
-        <v>50</v>
-      </c>
-      <c r="T12">
         <v>0.99850000000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="H13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
         <v>27</v>
       </c>
-      <c r="J13" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13">
-        <v>8.76</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>2.08</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>3</v>
-      </c>
-      <c r="R13">
-        <v>1000</v>
-      </c>
-      <c r="S13">
-        <v>50</v>
-      </c>
-      <c r="T13">
-        <v>0.63</v>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/vt_EST_PRI_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_PRI_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C750E11-AF57-47BD-955A-0FC101559EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A8C29E-A8F1-4E7B-A6F1-A237F55ACE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="36">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -87,9 +87,6 @@
     <t>Trd_electricity export_fi</t>
   </si>
   <si>
-    <t>~FI_T: USD21~FX~ACT_BND</t>
-  </si>
-  <si>
     <t>Process</t>
   </si>
   <si>
@@ -123,12 +120,12 @@
     <t>Trd_electricity export_ru</t>
   </si>
   <si>
-    <t>~FI_T: USD21~UP~ACT_BND</t>
-  </si>
-  <si>
     <t>NCAP_AFC!!!!</t>
   </si>
   <si>
+    <t>~FI_T:</t>
+  </si>
+  <si>
     <t>~FI_T</t>
   </si>
   <si>
@@ -141,7 +138,13 @@
     <t>ncap_pasti</t>
   </si>
   <si>
-    <t>~FI_T: UP</t>
+    <t>FI_Process</t>
+  </si>
+  <si>
+    <t>FI_T: USD21~FX~ACT_BND</t>
+  </si>
+  <si>
+    <t>FI_T: USD21~UP~ACT_BND</t>
   </si>
 </sst>
 </file>
@@ -507,10 +510,10 @@
   <sheetData>
     <row r="3" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -537,22 +540,22 @@
         <v>6</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" t="s">
         <v>19</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>20</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="O4" s="2">
         <v>2022</v>
@@ -564,13 +567,13 @@
         <v>0</v>
       </c>
       <c r="R4" t="s">
+        <v>22</v>
+      </c>
+      <c r="S4" t="s">
         <v>23</v>
       </c>
-      <c r="S4" t="s">
-        <v>24</v>
-      </c>
       <c r="V4" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.35">
@@ -593,7 +596,7 @@
         <v>12</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M5">
         <v>8.76</v>
@@ -634,7 +637,7 @@
         <v>13</v>
       </c>
       <c r="K6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M6">
         <v>8.76</v>
@@ -660,7 +663,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
@@ -672,10 +675,10 @@
         <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M7">
         <v>8.76</v>
@@ -730,7 +733,7 @@
         <v>10</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
@@ -738,7 +741,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>8</v>
@@ -750,22 +753,22 @@
         <v>10</v>
       </c>
       <c r="I10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" t="s">
         <v>19</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>20</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="O10" s="2">
         <v>2022</v>
@@ -777,10 +780,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="s">
+        <v>22</v>
+      </c>
+      <c r="S10" t="s">
         <v>23</v>
-      </c>
-      <c r="S10" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
@@ -788,7 +791,7 @@
         <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M11">
         <v>8.76</v>
@@ -814,7 +817,7 @@
         <v>14</v>
       </c>
       <c r="J12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M12">
         <v>8.76</v>
@@ -837,10 +840,10 @@
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="I13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M13">
         <v>8.76</v>
@@ -885,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -912,40 +915,40 @@
         <v>6</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" t="s">
         <v>19</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>20</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" t="s">
         <v>22</v>
       </c>
-      <c r="O4" s="2">
-        <v>0</v>
-      </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>23</v>
       </c>
-      <c r="Q4" t="s">
-        <v>24</v>
-      </c>
       <c r="R4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.35">
@@ -965,13 +968,13 @@
         <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I5" t="s">
         <v>12</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M5">
         <v>8.76</v>
@@ -1009,13 +1012,13 @@
         <v>10</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I6" t="s">
         <v>13</v>
       </c>
       <c r="K6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M6">
         <v>8.76</v>
@@ -1053,7 +1056,7 @@
         <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.35">
@@ -1075,53 +1078,53 @@
     </row>
     <row r="9" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="K9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="H10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" t="s">
         <v>19</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>20</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="O10" s="2">
+        <v>0</v>
+      </c>
+      <c r="P10" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="2">
-        <v>0</v>
-      </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>23</v>
       </c>
-      <c r="Q10" t="s">
-        <v>24</v>
-      </c>
       <c r="R10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="H11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M11">
         <v>8.76</v>
@@ -1144,13 +1147,13 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="H12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12" t="s">
         <v>14</v>
       </c>
       <c r="J12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M12">
         <v>8.76</v>
@@ -1173,7 +1176,7 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="H13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.35">
@@ -1181,7 +1184,7 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>8</v>
@@ -1198,7 +1201,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>8</v>

--- a/VerveStacks_EST/vt_EST_PRI_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_PRI_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A8C29E-A8F1-4E7B-A6F1-A237F55ACE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E006480B-EC78-474E-9192-8DF2BE4DD168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="37">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -145,6 +145,9 @@
   </si>
   <si>
     <t>FI_T: USD21~UP~ACT_BND</t>
+  </si>
+  <si>
+    <t>ncap_af</t>
   </si>
 </sst>
 </file>
@@ -500,15 +503,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A3:V13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>33</v>
       </c>
@@ -520,7 +523,7 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -572,11 +575,14 @@
       <c r="S4" t="s">
         <v>23</v>
       </c>
+      <c r="T4" t="s">
+        <v>36</v>
+      </c>
       <c r="V4" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -601,6 +607,9 @@
       <c r="M5">
         <v>8.76</v>
       </c>
+      <c r="N5">
+        <v>40</v>
+      </c>
       <c r="O5">
         <v>6.86</v>
       </c>
@@ -616,8 +625,11 @@
       <c r="S5">
         <v>50</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="T5">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -642,6 +654,9 @@
       <c r="M6">
         <v>8.76</v>
       </c>
+      <c r="N6">
+        <v>10000</v>
+      </c>
       <c r="O6">
         <v>0</v>
       </c>
@@ -658,7 +673,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -699,7 +714,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -716,7 +731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -736,7 +751,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -786,7 +801,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I11" t="s">
         <v>15</v>
       </c>
@@ -812,7 +827,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I12" t="s">
         <v>14</v>
       </c>
@@ -838,7 +853,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="I13" t="s">
         <v>26</v>
       </c>
@@ -872,18 +887,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C768FA58-8399-45BE-8875-71A71258D648}">
   <dimension ref="A3:T17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -895,7 +910,7 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -951,7 +966,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -995,7 +1010,7 @@
         <v>1.016</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1039,7 +1054,7 @@
         <v>1.204</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1059,7 +1074,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1076,12 +1091,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K9" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H10" t="s">
         <v>30</v>
       </c>
@@ -1116,7 +1131,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H11" t="s">
         <v>31</v>
       </c>
@@ -1145,7 +1160,7 @@
         <v>1.016</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H12" t="s">
         <v>31</v>
       </c>
@@ -1174,12 +1189,12 @@
         <v>0.99850000000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="H13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1196,7 +1211,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>11</v>
       </c>

--- a/VerveStacks_EST/vt_EST_PRI_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_PRI_v1.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E006480B-EC78-474E-9192-8DF2BE4DD168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA3FEDE-457E-4A17-AA94-938421A69D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="36">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -121,9 +121,6 @@
   </si>
   <si>
     <t>NCAP_AFC!!!!</t>
-  </si>
-  <si>
-    <t>~FI_T:</t>
   </si>
   <si>
     <t>~FI_T</t>
@@ -501,6 +498,367 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C768FA58-8399-45BE-8875-71A71258D648}">
+  <dimension ref="A3:T17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>23</v>
+      </c>
+      <c r="R4" t="s">
+        <v>31</v>
+      </c>
+      <c r="S4" t="s">
+        <v>35</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5">
+        <v>40</v>
+      </c>
+      <c r="M5">
+        <v>8.76</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>3</v>
+      </c>
+      <c r="P5">
+        <v>1000</v>
+      </c>
+      <c r="Q5">
+        <v>50</v>
+      </c>
+      <c r="R5">
+        <v>1.016</v>
+      </c>
+      <c r="S5">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>10000</v>
+      </c>
+      <c r="M6">
+        <v>8.76</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>3</v>
+      </c>
+      <c r="P6">
+        <v>1000</v>
+      </c>
+      <c r="Q6">
+        <v>50</v>
+      </c>
+      <c r="R6">
+        <v>1.204</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K9" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="H10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" t="s">
+        <v>20</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0</v>
+      </c>
+      <c r="P10" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="H11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11">
+        <v>8.76</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>3</v>
+      </c>
+      <c r="P11">
+        <v>1000</v>
+      </c>
+      <c r="Q11">
+        <v>50</v>
+      </c>
+      <c r="R11">
+        <v>1.016</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="H12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12">
+        <v>8.76</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>3</v>
+      </c>
+      <c r="P12">
+        <v>1000</v>
+      </c>
+      <c r="Q12">
+        <v>50</v>
+      </c>
+      <c r="R12">
+        <v>0.99850000000000005</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="H13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A3:V13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -513,10 +871,10 @@
   <sheetData>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -576,7 +934,7 @@
         <v>23</v>
       </c>
       <c r="T4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V4" s="3" t="s">
         <v>27</v>
@@ -748,7 +1106,7 @@
         <v>10</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -877,355 +1235,6 @@
       </c>
       <c r="S13">
         <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C768FA58-8399-45BE-8875-71A71258D648}">
-  <dimension ref="A3:T17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" t="s">
-        <v>20</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O4" s="2">
-        <v>0</v>
-      </c>
-      <c r="P4" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>23</v>
-      </c>
-      <c r="R4" t="s">
-        <v>32</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5">
-        <v>8.76</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>3</v>
-      </c>
-      <c r="P5">
-        <v>1000</v>
-      </c>
-      <c r="Q5">
-        <v>50</v>
-      </c>
-      <c r="R5">
-        <v>1.016</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6">
-        <v>8.76</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>3</v>
-      </c>
-      <c r="P6">
-        <v>1000</v>
-      </c>
-      <c r="Q6">
-        <v>50</v>
-      </c>
-      <c r="R6">
-        <v>1.204</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K9" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L10" t="s">
-        <v>19</v>
-      </c>
-      <c r="M10" t="s">
-        <v>20</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O10" s="2">
-        <v>0</v>
-      </c>
-      <c r="P10" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H11" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11">
-        <v>8.76</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>3</v>
-      </c>
-      <c r="P11">
-        <v>1000</v>
-      </c>
-      <c r="Q11">
-        <v>50</v>
-      </c>
-      <c r="R11">
-        <v>1.016</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J12" t="s">
-        <v>24</v>
-      </c>
-      <c r="M12">
-        <v>8.76</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>3</v>
-      </c>
-      <c r="P12">
-        <v>1000</v>
-      </c>
-      <c r="Q12">
-        <v>50</v>
-      </c>
-      <c r="R12">
-        <v>0.99850000000000005</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="H13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/vt_EST_PRI_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_PRI_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA3FEDE-457E-4A17-AA94-938421A69D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A72A4B7A-EE69-4D49-9045-CFA0C1907343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="37">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -145,6 +145,9 @@
   </si>
   <si>
     <t>ncap_af</t>
+  </si>
+  <si>
+    <t>daynite</t>
   </si>
 </sst>
 </file>
@@ -596,7 +599,7 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
         <v>30</v>
@@ -646,7 +649,7 @@
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H6" t="s">
         <v>30</v>
@@ -693,7 +696,7 @@
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
         <v>30</v>
@@ -713,7 +716,7 @@
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">

--- a/VerveStacks_EST/vt_EST_PRI_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_PRI_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A72A4B7A-EE69-4D49-9045-CFA0C1907343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63861D47-8639-4D19-9D9A-F592033B1D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="39">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -148,6 +148,12 @@
   </si>
   <si>
     <t>daynite</t>
+  </si>
+  <si>
+    <t>Annual</t>
+  </si>
+  <si>
+    <t>~FI_T: EUR25</t>
   </si>
 </sst>
 </file>
@@ -502,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C768FA58-8399-45BE-8875-71A71258D648}">
-  <dimension ref="A3:T17"/>
+  <dimension ref="A3:V17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
@@ -514,19 +520,19 @@
     <col min="20" max="20" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -558,34 +564,34 @@
         <v>18</v>
       </c>
       <c r="L4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>22</v>
+      </c>
+      <c r="P4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R4" t="s">
+        <v>35</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="V4" t="s">
         <v>19</v>
       </c>
-      <c r="M4" t="s">
-        <v>20</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O4" s="2">
-        <v>0</v>
-      </c>
-      <c r="P4" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>23</v>
-      </c>
-      <c r="R4" t="s">
-        <v>31</v>
-      </c>
-      <c r="S4" t="s">
-        <v>35</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -611,31 +617,31 @@
         <v>24</v>
       </c>
       <c r="L5">
+        <v>8.76</v>
+      </c>
+      <c r="M5">
+        <v>40.49</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <v>1000</v>
+      </c>
+      <c r="P5">
+        <v>50</v>
+      </c>
+      <c r="Q5">
+        <v>1.016</v>
+      </c>
+      <c r="R5">
+        <v>0.8</v>
+      </c>
+      <c r="V5">
         <v>40</v>
       </c>
-      <c r="M5">
-        <v>8.76</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>3</v>
-      </c>
-      <c r="P5">
-        <v>1000</v>
-      </c>
-      <c r="Q5">
-        <v>50</v>
-      </c>
-      <c r="R5">
-        <v>1.016</v>
-      </c>
-      <c r="S5">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -649,7 +655,7 @@
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H6" t="s">
         <v>30</v>
@@ -661,28 +667,28 @@
         <v>24</v>
       </c>
       <c r="L6">
+        <v>8.76</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>1000</v>
+      </c>
+      <c r="P6">
+        <v>50</v>
+      </c>
+      <c r="Q6">
+        <v>1.204</v>
+      </c>
+      <c r="V6">
         <v>10000</v>
       </c>
-      <c r="M6">
-        <v>8.76</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>3</v>
-      </c>
-      <c r="P6">
-        <v>1000</v>
-      </c>
-      <c r="Q6">
-        <v>50</v>
-      </c>
-      <c r="R6">
-        <v>1.204</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -696,13 +702,13 @@
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -716,15 +722,15 @@
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K9" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="H10" t="s">
         <v>29</v>
       </c>
@@ -738,28 +744,28 @@
         <v>18</v>
       </c>
       <c r="L10" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>22</v>
+      </c>
+      <c r="P10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>31</v>
+      </c>
+      <c r="V10" t="s">
         <v>19</v>
       </c>
-      <c r="M10" t="s">
-        <v>20</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O10" s="2">
-        <v>0</v>
-      </c>
-      <c r="P10" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="H11" t="s">
         <v>30</v>
       </c>
@@ -769,26 +775,26 @@
       <c r="J11" t="s">
         <v>24</v>
       </c>
+      <c r="L11">
+        <v>8.76</v>
+      </c>
       <c r="M11">
-        <v>8.76</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O11">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="P11">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Q11">
-        <v>50</v>
-      </c>
-      <c r="R11">
         <v>1.016</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="H12" t="s">
         <v>30</v>
       </c>
@@ -798,31 +804,31 @@
       <c r="J12" t="s">
         <v>24</v>
       </c>
+      <c r="L12">
+        <v>8.76</v>
+      </c>
       <c r="M12">
-        <v>8.76</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O12">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="P12">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Q12">
-        <v>50</v>
-      </c>
-      <c r="R12">
         <v>0.99850000000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="H13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
